--- a/CHESS_floodwall_inputs.xlsx
+++ b/CHESS_floodwall_inputs.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\StormSim-Library\StormSim_Library\PSE_Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\CHESS-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A000F018-1A7F-438A-BF9A-71F8B08ABE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10778D87-9223-4904-88F7-7AF6EEA81B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="6645" windowWidth="28800" windowHeight="15255" xr2:uid="{392BD468-0951-485E-9EDB-F7D879C79477}"/>
+    <workbookView xWindow="4980" yWindow="4980" windowWidth="28800" windowHeight="15270"/>
   </bookViews>
   <sheets>
     <sheet name="FloodWall" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -462,48 +462,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -675,101 +675,103 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1088,17 +1090,17 @@
   <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="101.7109375" customWidth="1"/>
-    <col min="2" max="2" width="53.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="153.42578125" customWidth="1"/>
-    <col min="6" max="6" width="28.42578125" customWidth="1"/>
-    <col min="7" max="7" width="84.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="101.7109375" customWidth="true"/>
+    <col min="2" max="2" width="53.5703125" customWidth="true"/>
+    <col min="3" max="3" width="19.28515625" bestFit="true" customWidth="true"/>
+    <col min="4" max="4" width="63" customWidth="true"/>
+    <col min="6" max="6" width="28.42578125" customWidth="true"/>
+    <col min="7" max="7" width="84.28515625" bestFit="true" customWidth="true"/>
+    <col min="8" max="8" width="46.140625" customWidth="true"/>
+    <col min="9" max="9" width="13.5703125" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
         <v>111</v>
       </c>
@@ -1116,7 +1118,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>18</v>
       </c>
@@ -1142,7 +1144,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>110</v>
       </c>
@@ -1168,7 +1170,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>107</v>
       </c>
@@ -1194,7 +1196,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>104</v>
       </c>
@@ -1212,7 +1214,7 @@
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
     </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>101</v>
       </c>
@@ -1232,7 +1234,7 @@
       <c r="H6" s="28"/>
       <c r="I6" s="28"/>
     </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>98</v>
       </c>
@@ -1258,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>95</v>
       </c>
@@ -1284,7 +1286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>92</v>
       </c>
@@ -1310,7 +1312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>90</v>
       </c>
@@ -1336,7 +1338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>88</v>
       </c>
@@ -1362,7 +1364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>85</v>
       </c>
@@ -1373,14 +1375,14 @@
         <v>26</v>
       </c>
       <c r="D12" s="4">
-        <v>176.45</v>
+        <v>0</v>
       </c>
       <c r="F12" s="28"/>
       <c r="G12" s="28"/>
       <c r="H12" s="28"/>
       <c r="I12" s="28"/>
     </row>
-    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>83</v>
       </c>
@@ -1400,7 +1402,7 @@
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
     </row>
-    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>81</v>
       </c>
@@ -1426,7 +1428,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>79</v>
       </c>
@@ -1452,7 +1454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -1478,7 +1480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>73</v>
       </c>
@@ -1492,7 +1494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>69</v>
       </c>
@@ -1506,7 +1508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>64</v>
       </c>
@@ -1520,7 +1522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>61</v>
       </c>
@@ -1534,13 +1536,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" x14ac:dyDescent="0.25">
       <c r="A21" s="32"/>
       <c r="B21" s="31"/>
       <c r="C21" s="30"/>
       <c r="D21" s="30"/>
     </row>
-    <row r="22" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A22" s="29" t="s">
         <v>57</v>
       </c>
@@ -1548,7 +1550,7 @@
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
     </row>
-    <row r="23" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>18</v>
       </c>
@@ -1562,7 +1564,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>51</v>
       </c>
@@ -1576,7 +1578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>112</v>
       </c>
@@ -1590,7 +1592,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>43</v>
       </c>
@@ -1604,7 +1606,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>38</v>
       </c>
@@ -1618,13 +1620,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" x14ac:dyDescent="0.25">
       <c r="A28" s="23"/>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
     </row>
-    <row r="29" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A29" s="20" t="s">
         <v>35</v>
       </c>
@@ -1632,7 +1634,7 @@
       <c r="C29" s="22"/>
       <c r="D29" s="22"/>
     </row>
-    <row r="30" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>18</v>
       </c>
@@ -1646,7 +1648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
         <v>34</v>
       </c>
@@ -1660,7 +1662,7 @@
         <v>180.1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
@@ -1674,7 +1676,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" x14ac:dyDescent="0.25">
       <c r="A33" s="42" t="s">
         <v>30</v>
       </c>
@@ -1688,7 +1690,7 @@
         <v>176.2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" x14ac:dyDescent="0.25">
       <c r="A34" s="42" t="s">
         <v>28</v>
       </c>
@@ -1702,7 +1704,7 @@
         <v>175.8</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" x14ac:dyDescent="0.25">
       <c r="A35" s="42" t="s">
         <v>115</v>
       </c>
@@ -1716,7 +1718,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
         <v>117</v>
       </c>
@@ -1730,13 +1732,13 @@
         <v>173.99</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" x14ac:dyDescent="0.25">
       <c r="A37" s="20"/>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
       <c r="D37" s="20"/>
     </row>
-    <row r="38" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A38" s="19" t="s">
         <v>25</v>
       </c>
@@ -1744,7 +1746,7 @@
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
     </row>
-    <row r="39" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>18</v>
       </c>
@@ -1758,7 +1760,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>24</v>
       </c>
@@ -1772,7 +1774,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" ht="60.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>21</v>
       </c>
@@ -1786,13 +1788,13 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
       <c r="D42" s="10"/>
     </row>
-    <row r="43" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>19</v>
       </c>
@@ -1800,7 +1802,7 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
     </row>
-    <row r="44" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>18</v>
       </c>
@@ -1814,7 +1816,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>14</v>
       </c>
@@ -1828,7 +1830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>12</v>
       </c>
@@ -1842,7 +1844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>10</v>
       </c>
@@ -1856,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>8</v>
       </c>
@@ -1870,7 +1872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>6</v>
       </c>
@@ -1884,7 +1886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>4</v>
       </c>
@@ -1898,7 +1900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>2</v>
       </c>
@@ -1912,20 +1914,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" x14ac:dyDescent="0.25">
       <c r="A53" s="41"/>
     </row>
-    <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14.25" customHeight="true" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15" customHeight="true" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="19.5" customHeight="true" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection formatColumns="0" selectLockedCells="1"/>
+  <sheetProtection formatColumns="false" selectLockedCells="true"/>
   <protectedRanges>
     <protectedRange sqref="I15 I3:I4 I8:I11" name="Range1_1"/>
     <protectedRange sqref="D40:D41" name="Range1_1_4"/>

--- a/CHESS_floodwall_inputs.xlsx
+++ b/CHESS_floodwall_inputs.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\CHESS-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10778D87-9223-4904-88F7-7AF6EEA81B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5352DB8A-FD30-4E18-9DBD-3DDC545409F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="4980" windowWidth="28800" windowHeight="15270"/>
+    <workbookView xWindow="5670" yWindow="5610" windowWidth="28800" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FloodWall" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="117">
   <si>
     <t>NA</t>
   </si>
@@ -123,12 +123,6 @@
   </si>
   <si>
     <t>wall_bottom_elevation</t>
-  </si>
-  <si>
-    <t>Mound Toe Elevation (Negative Below Datum Zero)</t>
-  </si>
-  <si>
-    <t>toe_elevation</t>
   </si>
   <si>
     <t>Crest Width/Wall Width</t>
@@ -462,48 +456,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999938962981"/>
+        <fgColor theme="4" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981"/>
+        <fgColor theme="9" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.5999938962981"/>
+        <fgColor theme="7" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.5999938962981"/>
+        <fgColor theme="8" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981"/>
+        <fgColor theme="5" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5999938962981"/>
+        <fgColor theme="6" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -675,103 +669,101 @@
       </bottom>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="true" applyAlignment="true">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1090,40 +1082,40 @@
   <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="101.7109375" customWidth="true"/>
-    <col min="2" max="2" width="53.5703125" customWidth="true"/>
-    <col min="3" max="3" width="19.28515625" bestFit="true" customWidth="true"/>
-    <col min="4" max="4" width="63" customWidth="true"/>
-    <col min="6" max="6" width="28.42578125" customWidth="true"/>
-    <col min="7" max="7" width="84.28515625" bestFit="true" customWidth="true"/>
-    <col min="8" max="8" width="46.140625" customWidth="true"/>
-    <col min="9" max="9" width="13.5703125" bestFit="true" customWidth="true"/>
+    <col min="1" max="1" width="101.7109375" customWidth="1"/>
+    <col min="2" max="2" width="53.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" customWidth="1"/>
+    <col min="7" max="7" width="84.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="F1" s="39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G1" s="34"/>
       <c r="H1" s="34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I1" s="34" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -1144,24 +1136,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H3" s="36" t="s">
         <v>0</v>
@@ -1170,82 +1162,82 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I4" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="34"/>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
     </row>
-    <row r="6" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G6" s="28"/>
       <c r="H6" s="28"/>
       <c r="I6" s="28"/>
     </row>
-    <row r="7" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>18</v>
@@ -1260,24 +1252,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H8" s="16" t="s">
         <v>0</v>
@@ -1286,12 +1278,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>0</v>
@@ -1300,10 +1292,10 @@
         <v>1</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>0</v>
@@ -1312,12 +1304,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>0</v>
@@ -1326,10 +1318,10 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>0</v>
@@ -1338,24 +1330,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>26</v>
@@ -1364,12 +1356,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>26</v>
@@ -1382,12 +1374,12 @@
       <c r="H12" s="28"/>
       <c r="I12" s="28"/>
     </row>
-    <row r="13" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>0</v>
@@ -1396,18 +1388,18 @@
         <v>0</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G13" s="26"/>
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
     </row>
-    <row r="14" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>0</v>
@@ -1428,12 +1420,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>0</v>
@@ -1442,10 +1434,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H15" s="16" t="s">
         <v>0</v>
@@ -1454,12 +1446,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>0</v>
@@ -1468,10 +1460,10 @@
         <v>1</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>0</v>
@@ -1480,12 +1472,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>0</v>
@@ -1494,12 +1486,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>0</v>
@@ -1508,12 +1500,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>0</v>
@@ -1522,40 +1514,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>0</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="32"/>
       <c r="B21" s="31"/>
       <c r="C21" s="30"/>
       <c r="D21" s="30"/>
     </row>
-    <row r="22" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B22" s="23"/>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
     </row>
-    <row r="23" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>16</v>
@@ -1564,77 +1556,77 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D24" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="B25" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="23"/>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
     </row>
-    <row r="29" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
       <c r="D29" s="22"/>
     </row>
-    <row r="30" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>18</v>
       </c>
@@ -1648,12 +1640,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>26</v>
@@ -1662,12 +1654,12 @@
         <v>180.1</v>
       </c>
     </row>
-    <row r="32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>26</v>
@@ -1676,152 +1668,152 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="42" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D33" s="16">
-        <v>176.2</v>
-      </c>
-    </row>
-    <row r="34" x14ac:dyDescent="0.25">
+        <v>175.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="42" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="C34" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D34" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="16">
-        <v>175.8</v>
-      </c>
-    </row>
-    <row r="35" x14ac:dyDescent="0.25">
-      <c r="A35" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D35" s="16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" x14ac:dyDescent="0.25">
-      <c r="A36" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="B36" t="s">
-        <v>118</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D36" s="15">
+      <c r="D35" s="15">
         <v>173.99</v>
       </c>
     </row>
-    <row r="37" x14ac:dyDescent="0.25">
-      <c r="A37" s="20"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-    </row>
-    <row r="38" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
-      <c r="A38" s="19" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-    </row>
-    <row r="39" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B38" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C38" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D38" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="40" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B39" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D39" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="41" ht="60.75" thickBot="true" x14ac:dyDescent="0.3">
-      <c r="A41" s="14" t="s">
+    <row r="40" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B40" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="11">
+      <c r="C40" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="11">
         <v>0.9</v>
       </c>
     </row>
-    <row r="42" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-    </row>
-    <row r="43" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
-      <c r="A43" s="9" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+    </row>
+    <row r="42" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-    </row>
-    <row r="44" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B43" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C43" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D43" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>0</v>
@@ -1830,40 +1822,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D46" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="47" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D47" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>0</v>
@@ -1872,12 +1864,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>0</v>
@@ -1886,51 +1878,37 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="4">
+    <row r="50" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="14" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B51" s="14" t="s">
+      <c r="C50" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="21">
         <v>1</v>
       </c>
-      <c r="C51" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D51" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-    </row>
-    <row r="53" x14ac:dyDescent="0.25">
-      <c r="A53" s="41"/>
-    </row>
-    <row r="54" ht="14.25" customHeight="true" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15" customHeight="true" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="19.5" customHeight="true" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="41"/>
+    </row>
+    <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection formatColumns="false" selectLockedCells="true"/>
+  <sheetProtection formatColumns="0" selectLockedCells="1"/>
   <protectedRanges>
     <protectedRange sqref="I15 I3:I4 I8:I11" name="Range1_1"/>
-    <protectedRange sqref="D40:D41" name="Range1_1_4"/>
+    <protectedRange sqref="D39:D40" name="Range1_1_4"/>
     <protectedRange sqref="D14 D16:D18 D9:D12 D6" name="Range1_1_1"/>
     <protectedRange sqref="D8 D15" name="Range1_1_1_1"/>
     <protectedRange sqref="D13" name="Range1_1_2"/>
@@ -1939,12 +1917,11 @@
     <protectedRange sqref="D5" name="Range1_1_7"/>
     <protectedRange sqref="D7" name="Range1_1_5"/>
     <protectedRange sqref="D31" name="Range1_1_3_1_3"/>
-    <protectedRange sqref="D34" name="Range1_1_3_1_1"/>
+    <protectedRange sqref="D33" name="Range1_1_3_1_1"/>
     <protectedRange sqref="D32" name="Range1_1_3_1_4"/>
-    <protectedRange sqref="D33" name="Range1_1_3_1_5"/>
     <protectedRange sqref="D24" name="Range1_1_3_3_2"/>
     <protectedRange sqref="D27" name="Range1_1_2_1_1_2"/>
-    <protectedRange sqref="D36 D25" name="Range1_1_5_2_2"/>
+    <protectedRange sqref="D35 D25" name="Range1_1_5_2_2"/>
     <protectedRange sqref="D26" name="Range1_1_8_1_1_2"/>
   </protectedRanges>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
